--- a/content.xlsx
+++ b/content.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8115" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8115"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
   <si>
     <t>title</t>
   </si>
@@ -104,6 +104,15 @@
   </si>
   <si>
     <t>Analysis of contrarian claims on twitter</t>
+  </si>
+  <si>
+    <t>dod-eth.png</t>
+  </si>
+  <si>
+    <t>https://keep-it-cool.ethz.ch/en/solutions/society/climate-excuses</t>
+  </si>
+  <si>
+    <t>An online version of the exhibit at Frankfurt's Museum of Communication.</t>
   </si>
 </sst>
 </file>
@@ -432,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
@@ -516,6 +525,17 @@
       </c>
       <c r="D7" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
